--- a/assets/constructions/examples/ctd_mie_corn901.xlsx
+++ b/assets/constructions/examples/ctd_mie_corn901.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,61 +584,85 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R200-D40-32-55-125-18</t>
+          <t>MT190L-050W50R04SO09-100-IK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R200</t>
+          <t>MT190L-W...SO09...IK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
+        <v>205</v>
+      </c>
+      <c r="H2" t="n">
         <v>125</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>13500</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q2" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>APKT1003</t>
+          <t>BO..12T3.. + SO..09T308..</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -646,12 +670,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HB-50</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>LIKON_AP1003H</t>
+          <t>SKIF_BO12T3H + SKIF_SO09T3H</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -664,82 +688,84 @@
         <v>90</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>LIK_AP1003H</t>
+          <t>SKIF_BO12T3H + SKIF_SO09T3H</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2019/ Основной каталог СКИФ-М</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT190L-050W50R04SD08/BD12-074-IK</t>
+          <t>R200-D25-25-37-120-8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MT190L-W...SD08/BD12...IK</t>
+          <t>R200</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>180</v>
-      </c>
-      <c r="H3" t="n">
-        <v>100</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>13500</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.2</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>BDMT1204.. + SD.T08T308.R</t>
+          <t>APKT1003</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -747,12 +773,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HB-50</t>
+          <t>HA-25</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SKIF_BD1204H + SKIF_SD08T3H</t>
+          <t>LIKON_AP1003H</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -765,127 +791,141 @@
         <v>90</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>SKIF_BD1204H + SKIF_SD08T3H</t>
+          <t>LIK_AP1003H</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APE-C25-25-125-2T</t>
+          <t>MT190L-040W40R03SD08/BD12-087-IK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>APE</t>
+          <t>MT190L-W...SD08/BD12...IK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="H4" t="n">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>87</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>BDMT1204.. + SD.T08T308.R</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>HB-40</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SKIF_BD1204H + SKIF_SD08T3H</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>37</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>APKX1003</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>HB-25</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>DER_APKX1003H</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
       </c>
       <c r="Y4" t="n">
         <v>90</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>AP1003_H</t>
+          <t>SKIF_BD1204H + SKIF_SD08T3H</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2019/ Основной каталог СКИФ-М</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT190L-032W32R02SD08-38</t>
+          <t>MT190L-032W32R03BD10-53-IK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -895,7 +935,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT190L-W...SD08</t>
+          <t>MT190L-W...BD10-IK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -906,31 +946,31 @@
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>13200</v>
+        <v>26000</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -939,7 +979,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>SD.T08T308.R</t>
+          <t>BDMT10T3..</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -952,28 +992,28 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SKIF_SD0803H</t>
+          <t>SKIF_BD10T3H</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
         <v>90</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>SKIF_SD0803H</t>
+          <t>SKIF_BD10T3H</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -982,56 +1022,60 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT190L-040W32R03SD08-45</t>
+          <t>APE-C20-20-107-2T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>СКИФ-М</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MT190L-W...SD08</t>
+          <t>APE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>11300</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1040,7 +1084,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>SD.T08T308.R</t>
+          <t>APKX1003</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1048,12 +1092,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>HB-32</t>
+          <t>HB-20</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SKIF_SD0803H</t>
+          <t>DER_APKX1003H</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1074,15 +1118,21 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>SKIF_SD0803H</t>
+          <t>AP1003_H</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2019/ Основной каталог СКИФ-М</t>
-        </is>
-      </c>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
